--- a/MainTop/18.09.2026 3гор/Петербург_p1.xlsx
+++ b/MainTop/18.09.2026 3гор/Петербург_p1.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -583,7 +583,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -639,7 +639,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -751,7 +751,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -863,7 +863,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L51" t="n">
